--- a/artfynd/A 56294-2022 artfynd.xlsx
+++ b/artfynd/A 56294-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56294-2022 artfynd.xlsx
+++ b/artfynd/A 56294-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,118 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120541603</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105113</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skäpperöd, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>420362</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6163604</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sövde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Ängsbokskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alex Regnér, Viktor Nilsson, Kristian Nilsson, Gunilla Davidsson Lundh, Magnus Berglund, Pernilla Olsson, Eva Ohlsson, Cecilia Backe, Jenny Hall, Johan Johnmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56294-2022 artfynd.xlsx
+++ b/artfynd/A 56294-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>270585</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420418.7324402877</v>
+        <v>420419</v>
       </c>
       <c r="R2" t="n">
-        <v>6163696.612529298</v>
+        <v>6163697</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,7 +740,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>M-Sbo-0064</t>
+          <t>Arkiv-M-Sbo-0020</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -753,19 +748,9 @@
           <t>1992-07-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,43 +785,38 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120541603</v>
+        <v>120541679</v>
       </c>
       <c r="B3" t="n">
-        <v>105240</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221423</v>
+        <v>178</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Huds.) Holub</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skäpperöd, Sk</t>
+          <t>Skäpperöds källbäckar, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420362</v>
+        <v>420390</v>
       </c>
       <c r="R3" t="n">
-        <v>6163604</v>
+        <v>6163732</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +880,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Ängsbokskog</t>
+          <t>Ängsädellövskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Översilad</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,6 +900,225 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120541660</v>
+      </c>
+      <c r="B4" t="n">
+        <v>46984</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102887</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Curtis, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skäpperöds källbäckar, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420390</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6163732</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sövde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>i ädellövskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alex Regnér, Viktor Nilsson, Kristian Nilsson, Gunilla Davidsson Lundh, Magnus Berglund, Pernilla Olsson, Eva Ohlsson, Cecilia Backe, Jenny Hall, Johan Johnmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120541603</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skäpperöd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>420362</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6163604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sövde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ängsbokskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alex Regnér, Viktor Nilsson, Kristian Nilsson, Gunilla Davidsson Lundh, Magnus Berglund, Pernilla Olsson, Eva Ohlsson, Cecilia Backe, Jenny Hall, Johan Johnmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
